--- a/specifications/ig/all-profiles.xlsx
+++ b/specifications/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:37:54+00:00</t>
+    <t>2026-06-29T15:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specifications/ig/all-profiles.xlsx
+++ b/specifications/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:13:18+00:00</t>
+    <t>2026-07-01T07:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/specifications/ig/all-profiles.xlsx
+++ b/specifications/ig/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T07:07:10+00:00</t>
+    <t>2026-07-01T07:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
